--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,34 +436,630 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
+          <t>ABADIA SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ARAGON</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BAVIERA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BURDEOS CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BURGOS CASTILLA RESERVADO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CADIZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EL CAMPO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EL CASTELL IBERIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GALLET CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LA CABRERA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LA CRUZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LA PALMA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LA PEÑA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LA SCALA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LA TERRA ALSACIA RESERVADO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LINZ E1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOIRA CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LORCA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LYON 2 CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LYON CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>METROPOLI 30</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PASEO DE SEVILLA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PASEO SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PEÑAZUL EL POBLADO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PEÑON DE ALICANTE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PROVENZA PRESTIGE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SAN LUCAS LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SAN MATEO - LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>URBANISMO EXTERNO LOTE 5 BANCA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ZURI - ZENTRAL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MALAGA CASTILLA RESERVADO</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PRUEBA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA CRISTALINA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AMARETTO</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RIVERBAY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PARQUE ORIENTE SOLEIL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,17 +429,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -996,55 +996,19 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>PUERTA DORADA CRISTALINA</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AMARETTO</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>RIVERBAY</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,38 +995,6 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>PARQUE ORIENTE SOLEIL</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
